--- a/reports/pro-crypto/pro-crypto-bundler-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-bundler-report.xlsx
@@ -167,36 +167,42 @@
     <x:t>ANDERSON</x:t>
   </x:si>
   <x:si>
+    <x:t>C00821082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIGITAL FUTURE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANDREESSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00824896</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLOCKCHAIN ASSOCIATION POLITICAL ACTION COMMITTEE (BA PAC)</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00852657</x:t>
   </x:si>
   <x:si>
     <x:t>KEEP STARTUPS IN AMERICA</x:t>
   </x:si>
   <x:si>
-    <x:t>MARC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANDREESSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00824896</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLOCKCHAIN ASSOCIATION POLITICAL ACTION COMMITTEE (BA PAC)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00821082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DIGITAL FUTURE PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>LUWAM</x:t>
   </x:si>
   <x:si>
     <x:t>AREFE</x:t>
   </x:si>
   <x:si>
+    <x:t>C00835959</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIRSHAKE</x:t>
+  </x:si>
+  <x:si>
     <x:t>BRIAN</x:t>
   </x:si>
   <x:si>
@@ -206,12 +212,6 @@
     <x:t>SAN FRANCISCO</x:t>
   </x:si>
   <x:si>
-    <x:t>C00835959</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIRSHAKE</x:t>
-  </x:si>
-  <x:si>
     <x:t>LAURA</x:t>
   </x:si>
   <x:si>
@@ -890,12 +890,12 @@
     <x:t>ESTES</x:t>
   </x:si>
   <x:si>
+    <x:t>GOLDEN OAK</x:t>
+  </x:si>
+  <x:si>
     <x:t>ORLANDO</x:t>
   </x:si>
   <x:si>
-    <x:t>GOLDEN OAK</x:t>
-  </x:si>
-  <x:si>
     <x:t>OPUTA</x:t>
   </x:si>
   <x:si>
@@ -2294,31 +2294,31 @@
     <x:t>committees_supported</x:t>
   </x:si>
   <x:si>
+    <x:t>FAIRSHAKE,FIRST PRINCIPLES DIGITAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>FIRST PRINCIPLES DIGITAL,FAIRSHAKE</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIRSHAKE,FIRST PRINCIPLES DIGITAL</x:t>
+    <x:t>COINBASE, INC. INNOVATION PAC (COINBASE INNOVATION PAC),FAIRSHAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLOCKCHAIN ASSOCIATION POLITICAL ACTION COMMITTEE (BA PAC),KEEP STARTUPS IN AMERICA,DIGITAL FUTURE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLOCKCHAIN ASSOCIATION POLITICAL ACTION COMMITTEE (BA PAC),KEEP STARTUPS IN AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KEEP STARTUPS IN AMERICA,BLOCKCHAIN ASSOCIATION POLITICAL ACTION COMMITTEE (BA PAC)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIGITAL FUTURE PAC,BLOCKCHAIN ASSOCIATION POLITICAL ACTION COMMITTEE (BA PAC)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COINBASE, INC. INNOVATION PAC (COINBASE INNOVATION PAC),STAND WITH CRYPTO ALLIANCE, INC. POLITICAL ACTION COMMITTEE</x:t>
   </x:si>
   <x:si>
     <x:t>FAIRSHAKE,COINBASE, INC. INNOVATION PAC (COINBASE INNOVATION PAC)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLOCKCHAIN ASSOCIATION POLITICAL ACTION COMMITTEE (BA PAC),KEEP STARTUPS IN AMERICA,DIGITAL FUTURE PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KEEP STARTUPS IN AMERICA,BLOCKCHAIN ASSOCIATION POLITICAL ACTION COMMITTEE (BA PAC)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLOCKCHAIN ASSOCIATION POLITICAL ACTION COMMITTEE (BA PAC),KEEP STARTUPS IN AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DIGITAL FUTURE PAC,BLOCKCHAIN ASSOCIATION POLITICAL ACTION COMMITTEE (BA PAC)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STAND WITH CRYPTO ALLIANCE, INC. POLITICAL ACTION COMMITTEE,COINBASE, INC. INNOVATION PAC (COINBASE INNOVATION PAC)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COINBASE, INC. INNOVATION PAC (COINBASE INNOVATION PAC),FAIRSHAKE</x:t>
   </x:si>
   <x:si>
     <x:t>FAIRSHAKE,STAND WITH CRYPTO ALLIANCE, INC. POLITICAL ACTION COMMITTEE</x:t>
@@ -6946,7 +6946,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="G14" s="1">
-        <x:v>20000</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
@@ -6992,7 +6992,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="G16" s="1">
-        <x:v>5000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
@@ -7020,48 +7020,48 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="G18" s="1">
-        <x:v>5000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B19" s="1" t="s">
+      <x:c r="E19" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="C19" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D19" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="F19" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="G19" s="1">
-        <x:v>1000000</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
@@ -7072,10 +7072,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>11</x:v>
@@ -7089,10 +7089,10 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>63</x:v>
@@ -7107,15 +7107,15 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="G21" s="1">
-        <x:v>20000</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>63</x:v>
@@ -7130,7 +7130,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="G22" s="1">
-        <x:v>5000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
@@ -7503,10 +7503,10 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>107</x:v>
@@ -7515,7 +7515,7 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
         <x:v>12</x:v>
@@ -7687,10 +7687,10 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>123</x:v>
@@ -7699,7 +7699,7 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
         <x:v>12</x:v>
@@ -7779,10 +7779,10 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
         <x:v>130</x:v>
@@ -7917,10 +7917,10 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
         <x:v>146</x:v>
@@ -8101,10 +8101,10 @@
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
         <x:v>167</x:v>
@@ -8113,7 +8113,7 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F65" s="1" t="s">
         <x:v>12</x:v>
@@ -8147,10 +8147,10 @@
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
         <x:v>174</x:v>
@@ -8239,10 +8239,10 @@
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
         <x:v>184</x:v>
@@ -8285,10 +8285,10 @@
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
         <x:v>189</x:v>
@@ -8498,7 +8498,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
         <x:v>208</x:v>
@@ -8596,7 +8596,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F86" s="1" t="s">
         <x:v>12</x:v>
@@ -8745,10 +8745,10 @@
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
         <x:v>69</x:v>
@@ -8837,10 +8837,10 @@
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
         <x:v>146</x:v>
@@ -9044,10 +9044,10 @@
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
         <x:v>256</x:v>
@@ -9067,10 +9067,10 @@
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
         <x:v>259</x:v>
@@ -9090,10 +9090,10 @@
     </x:row>
     <x:row r="108" spans="1:7">
       <x:c r="A108" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
         <x:v>259</x:v>
@@ -9113,10 +9113,10 @@
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
         <x:v>259</x:v>
@@ -9228,10 +9228,10 @@
     </x:row>
     <x:row r="114" spans="1:7">
       <x:c r="A114" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B114" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C114" s="1" t="s">
         <x:v>174</x:v>
@@ -9435,13 +9435,13 @@
     </x:row>
     <x:row r="123" spans="1:7">
       <x:c r="A123" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B123" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C123" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D123" s="1" t="s">
         <x:v>288</x:v>
@@ -9453,18 +9453,18 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="G123" s="1">
-        <x:v>10000</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:7">
       <x:c r="A124" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B124" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C124" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D124" s="1" t="s">
         <x:v>288</x:v>
@@ -9476,7 +9476,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="G124" s="1">
-        <x:v>5000</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:7">
@@ -9964,10 +9964,10 @@
     </x:row>
     <x:row r="146" spans="1:7">
       <x:c r="A146" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B146" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
         <x:v>327</x:v>
@@ -10102,10 +10102,10 @@
     </x:row>
     <x:row r="152" spans="1:7">
       <x:c r="A152" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B152" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C152" s="1" t="s">
         <x:v>342</x:v>
@@ -10114,7 +10114,7 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="E152" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F152" s="1" t="s">
         <x:v>12</x:v>
@@ -10286,10 +10286,10 @@
     </x:row>
     <x:row r="160" spans="1:7">
       <x:c r="A160" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B160" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C160" s="1" t="s">
         <x:v>357</x:v>
@@ -10723,10 +10723,10 @@
     </x:row>
     <x:row r="179" spans="1:7">
       <x:c r="A179" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B179" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C179" s="1" t="s">
         <x:v>280</x:v>
@@ -10741,15 +10741,15 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="G179" s="1">
-        <x:v>20000</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:7">
       <x:c r="A180" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B180" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C180" s="1" t="s">
         <x:v>280</x:v>
@@ -10764,15 +10764,15 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="G180" s="1">
-        <x:v>10000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:7">
       <x:c r="A181" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B181" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C181" s="1" t="s">
         <x:v>136</x:v>
@@ -10815,10 +10815,10 @@
     </x:row>
     <x:row r="183" spans="1:7">
       <x:c r="A183" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B183" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C183" s="1" t="s">
         <x:v>396</x:v>
@@ -10838,10 +10838,10 @@
     </x:row>
     <x:row r="184" spans="1:7">
       <x:c r="A184" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B184" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C184" s="1" t="s">
         <x:v>397</x:v>
@@ -10850,7 +10850,7 @@
         <x:v>398</x:v>
       </x:c>
       <x:c r="E184" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F184" s="1" t="s">
         <x:v>12</x:v>
@@ -10896,7 +10896,7 @@
         <x:v>403</x:v>
       </x:c>
       <x:c r="E186" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F186" s="1" t="s">
         <x:v>12</x:v>
@@ -11114,10 +11114,10 @@
     </x:row>
     <x:row r="196" spans="1:7">
       <x:c r="A196" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B196" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C196" s="1" t="s">
         <x:v>107</x:v>
@@ -11689,10 +11689,10 @@
     </x:row>
     <x:row r="221" spans="1:7">
       <x:c r="A221" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B221" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C221" s="1" t="s">
         <x:v>236</x:v>
@@ -11735,10 +11735,10 @@
     </x:row>
     <x:row r="223" spans="1:7">
       <x:c r="A223" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B223" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C223" s="1" t="s">
         <x:v>96</x:v>
@@ -11954,13 +11954,13 @@
         <x:v>488</x:v>
       </x:c>
       <x:c r="E232" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="F232" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="G232" s="1">
-        <x:v>15000</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="233" spans="1:7">
@@ -11977,13 +11977,13 @@
         <x:v>488</x:v>
       </x:c>
       <x:c r="E233" s="1" t="s">
-        <x:v>489</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F233" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G233" s="1">
-        <x:v>5000</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="234" spans="1:7">
@@ -12126,10 +12126,10 @@
     </x:row>
     <x:row r="240" spans="1:7">
       <x:c r="A240" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B240" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C240" s="1" t="s">
         <x:v>69</x:v>
@@ -12195,10 +12195,10 @@
     </x:row>
     <x:row r="243" spans="1:7">
       <x:c r="A243" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B243" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C243" s="1" t="s">
         <x:v>315</x:v>
@@ -12425,10 +12425,10 @@
     </x:row>
     <x:row r="253" spans="1:7">
       <x:c r="A253" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B253" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C253" s="1" t="s">
         <x:v>31</x:v>
@@ -12793,10 +12793,10 @@
     </x:row>
     <x:row r="269" spans="1:7">
       <x:c r="A269" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B269" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C269" s="1" t="s">
         <x:v>552</x:v>
@@ -12816,10 +12816,10 @@
     </x:row>
     <x:row r="270" spans="1:7">
       <x:c r="A270" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B270" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C270" s="1" t="s">
         <x:v>554</x:v>
@@ -12931,10 +12931,10 @@
     </x:row>
     <x:row r="275" spans="1:7">
       <x:c r="A275" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B275" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C275" s="1" t="s">
         <x:v>565</x:v>
@@ -13035,7 +13035,7 @@
         <x:v>574</x:v>
       </x:c>
       <x:c r="E279" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F279" s="1" t="s">
         <x:v>12</x:v>
@@ -13052,7 +13052,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C280" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D280" s="1" t="s">
         <x:v>575</x:v>
@@ -13150,7 +13150,7 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="E284" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F284" s="1" t="s">
         <x:v>12</x:v>
@@ -13161,10 +13161,10 @@
     </x:row>
     <x:row r="285" spans="1:7">
       <x:c r="A285" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B285" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C285" s="1" t="s">
         <x:v>580</x:v>
@@ -13173,21 +13173,21 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="E285" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F285" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="G285" s="1">
-        <x:v>5000</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="286" spans="1:7">
       <x:c r="A286" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B286" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C286" s="1" t="s">
         <x:v>580</x:v>
@@ -13196,21 +13196,21 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="E286" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F286" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="G286" s="1">
-        <x:v>10000</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="287" spans="1:7">
       <x:c r="A287" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B287" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C287" s="1" t="s">
         <x:v>582</x:v>
@@ -14208,21 +14208,21 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="E330" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F330" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G330" s="1">
-        <x:v>15000</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="331" spans="1:7">
       <x:c r="A331" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B331" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C331" s="1" t="s">
         <x:v>659</x:v>
@@ -14242,10 +14242,10 @@
     </x:row>
     <x:row r="332" spans="1:7">
       <x:c r="A332" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B332" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C332" s="1" t="s">
         <x:v>659</x:v>
@@ -14254,13 +14254,13 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="E332" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F332" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G332" s="1">
-        <x:v>5000</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="333" spans="1:7">
@@ -14288,10 +14288,10 @@
     </x:row>
     <x:row r="334" spans="1:7">
       <x:c r="A334" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B334" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C334" s="1" t="s">
         <x:v>662</x:v>
@@ -14587,13 +14587,13 @@
     </x:row>
     <x:row r="347" spans="1:7">
       <x:c r="A347" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B347" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C347" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D347" s="1" t="s">
         <x:v>681</x:v>
@@ -14771,10 +14771,10 @@
     </x:row>
     <x:row r="355" spans="1:7">
       <x:c r="A355" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B355" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C355" s="1" t="s">
         <x:v>694</x:v>
@@ -15070,10 +15070,10 @@
     </x:row>
     <x:row r="368" spans="1:7">
       <x:c r="A368" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B368" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C368" s="1" t="s">
         <x:v>134</x:v>
@@ -15254,10 +15254,10 @@
     </x:row>
     <x:row r="376" spans="1:7">
       <x:c r="A376" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B376" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C376" s="1" t="s">
         <x:v>71</x:v>
@@ -15346,10 +15346,10 @@
     </x:row>
     <x:row r="380" spans="1:7">
       <x:c r="A380" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B380" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C380" s="1" t="s">
         <x:v>732</x:v>
@@ -15369,10 +15369,10 @@
     </x:row>
     <x:row r="381" spans="1:7">
       <x:c r="A381" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B381" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C381" s="1" t="s">
         <x:v>730</x:v>
@@ -15392,10 +15392,10 @@
     </x:row>
     <x:row r="382" spans="1:7">
       <x:c r="A382" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B382" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C382" s="1" t="s">
         <x:v>732</x:v>
@@ -15438,10 +15438,10 @@
     </x:row>
     <x:row r="384" spans="1:7">
       <x:c r="A384" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B384" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C384" s="1" t="s">
         <x:v>730</x:v>
@@ -15456,15 +15456,15 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G384" s="1">
-        <x:v>496602</x:v>
+        <x:v>2450000</x:v>
       </x:c>
     </x:row>
     <x:row r="385" spans="1:7">
       <x:c r="A385" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B385" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="C385" s="1" t="s">
         <x:v>730</x:v>
@@ -15479,7 +15479,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G385" s="1">
-        <x:v>2450000</x:v>
+        <x:v>496602</x:v>
       </x:c>
     </x:row>
     <x:row r="386" spans="1:7">
@@ -15691,10 +15691,10 @@
     </x:row>
     <x:row r="395" spans="1:7">
       <x:c r="A395" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B395" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C395" s="1" t="s">
         <x:v>123</x:v>
@@ -15917,13 +15917,13 @@
     </x:row>
     <x:row r="4" spans="1:6">
       <x:c r="A4" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
         <x:v>12</x:v>
@@ -15952,7 +15952,7 @@
         <x:v>997971</x:v>
       </x:c>
       <x:c r="F5" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
@@ -15963,7 +15963,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>12</x:v>
@@ -15992,7 +15992,7 @@
         <x:v>300008</x:v>
       </x:c>
       <x:c r="F7" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
@@ -16032,7 +16032,7 @@
         <x:v>250000</x:v>
       </x:c>
       <x:c r="F9" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6">
@@ -16092,7 +16092,7 @@
         <x:v>50000</x:v>
       </x:c>
       <x:c r="F12" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6">
@@ -16112,7 +16112,7 @@
         <x:v>50000</x:v>
       </x:c>
       <x:c r="F13" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6">
@@ -16212,7 +16212,7 @@
         <x:v>25000</x:v>
       </x:c>
       <x:c r="F18" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6">
@@ -16252,7 +16252,7 @@
         <x:v>25000</x:v>
       </x:c>
       <x:c r="F20" s="2" t="s">
-        <x:v>761</x:v>
+        <x:v>762</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6">
@@ -16263,7 +16263,7 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>12</x:v>
@@ -16272,7 +16272,7 @@
         <x:v>25000</x:v>
       </x:c>
       <x:c r="F21" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6">
@@ -16412,15 +16412,15 @@
         <x:v>20000</x:v>
       </x:c>
       <x:c r="F28" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6">
       <x:c r="A29" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>11</x:v>
@@ -16452,7 +16452,7 @@
         <x:v>20000</x:v>
       </x:c>
       <x:c r="F30" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
@@ -16797,7 +16797,7 @@
     </x:row>
     <x:row r="48" spans="1:6">
       <x:c r="A48" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
         <x:v>681</x:v>
@@ -16812,7 +16812,7 @@
         <x:v>15000</x:v>
       </x:c>
       <x:c r="F48" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:6">
@@ -17197,13 +17197,13 @@
     </x:row>
     <x:row r="68" spans="1:6">
       <x:c r="A68" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
         <x:v>288</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
         <x:v>88</x:v>
@@ -17283,7 +17283,7 @@
         <x:v>398</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
         <x:v>12</x:v>
@@ -17292,7 +17292,7 @@
         <x:v>10000</x:v>
       </x:c>
       <x:c r="F72" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:6">
@@ -17483,7 +17483,7 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
         <x:v>12</x:v>
@@ -18272,7 +18272,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="F121" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:6">
@@ -18283,7 +18283,7 @@
         <x:v>574</x:v>
       </x:c>
       <x:c r="C122" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D122" s="1" t="s">
         <x:v>12</x:v>
@@ -18332,7 +18332,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="F124" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:6">
@@ -18357,7 +18357,7 @@
     </x:row>
     <x:row r="126" spans="1:6">
       <x:c r="A126" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B126" s="1" t="s">
         <x:v>208</x:v>
@@ -18377,13 +18377,13 @@
     </x:row>
     <x:row r="127" spans="1:6">
       <x:c r="A127" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B127" s="1" t="s">
         <x:v>288</x:v>
       </x:c>
       <x:c r="C127" s="1" t="s">
-        <x:v>290</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D127" s="1" t="s">
         <x:v>88</x:v>
@@ -18423,7 +18423,7 @@
         <x:v>403</x:v>
       </x:c>
       <x:c r="C129" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D129" s="1" t="s">
         <x:v>12</x:v>
@@ -18652,7 +18652,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="F140" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:6">
@@ -19232,7 +19232,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="F169" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:6">
@@ -19972,7 +19972,7 @@
         <x:v>2500</x:v>
       </x:c>
       <x:c r="F206" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:6">
@@ -20477,7 +20477,7 @@
     </x:row>
     <x:row r="232" spans="1:6">
       <x:c r="A232" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B232" s="1" t="s">
         <x:v>575</x:v>
@@ -20992,7 +20992,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="F257" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="258" spans="1:6">
@@ -21032,7 +21032,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="F259" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="260" spans="1:6">
@@ -21292,7 +21292,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="F272" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="273" spans="1:6">
@@ -21363,7 +21363,7 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="C276" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D276" s="1" t="s">
         <x:v>12</x:v>
@@ -21372,7 +21372,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="F276" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="277" spans="1:6">
@@ -21443,7 +21443,7 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="C280" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D280" s="1" t="s">
         <x:v>12</x:v>
@@ -21452,7 +21452,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="F280" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="281" spans="1:6">
@@ -21492,7 +21492,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="F282" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="283" spans="1:6">
@@ -21972,7 +21972,7 @@
         <x:v>680</x:v>
       </x:c>
       <x:c r="F306" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="307" spans="1:6">
@@ -22232,7 +22232,7 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="F319" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="320" spans="1:6">
@@ -22312,7 +22312,7 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="F323" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="324" spans="1:6">
@@ -22512,7 +22512,7 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="F333" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="334" spans="1:6">
@@ -22632,7 +22632,7 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="F339" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="340" spans="1:6">
@@ -22832,7 +22832,7 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="F349" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="350" spans="1:6">
@@ -23012,7 +23012,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="F358" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="359" spans="1:6">
@@ -23032,7 +23032,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="F359" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="360" spans="1:6">
@@ -23332,7 +23332,7 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="F374" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="375" spans="1:6">
@@ -23483,7 +23483,7 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="C382" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D382" s="1" t="s">
         <x:v>12</x:v>
@@ -23492,7 +23492,7 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="F382" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="383" spans="1:6">
@@ -23512,7 +23512,7 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="F383" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="384" spans="1:6">
@@ -23532,7 +23532,7 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="F384" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="385" spans="1:6">
@@ -23552,7 +23552,7 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="F385" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="386" spans="1:6">
@@ -23572,7 +23572,7 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="F386" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="387" spans="1:6">
@@ -23592,7 +23592,7 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="F387" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="388" spans="1:6">
@@ -23718,7 +23718,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I2" s="1">
         <x:v>5000</x:v>
@@ -23776,7 +23776,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H4" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>5000</x:v>
@@ -23805,7 +23805,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H5" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>25000</x:v>
@@ -23892,7 +23892,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H8" s="2" t="s">
-        <x:v>761</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>25000</x:v>
@@ -23979,7 +23979,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H11" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>25000</x:v>
@@ -24037,7 +24037,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H13" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>20000</x:v>
@@ -24124,7 +24124,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H16" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>25000</x:v>
@@ -24153,7 +24153,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H17" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>20000</x:v>
@@ -24240,7 +24240,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H20" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>20000</x:v>
@@ -24298,7 +24298,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H22" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>20000</x:v>
@@ -24327,7 +24327,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H23" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>5000</x:v>
@@ -24356,7 +24356,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H24" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>25000</x:v>
@@ -24379,7 +24379,7 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>12</x:v>
@@ -24501,7 +24501,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H29" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>5000</x:v>
@@ -24640,7 +24640,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -24663,13 +24663,13 @@
         <x:v>3500</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>12</x:v>
@@ -24791,7 +24791,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H39" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>25000</x:v>
@@ -24907,7 +24907,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H43" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>25000</x:v>
@@ -24936,7 +24936,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H44" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>20000</x:v>
@@ -25023,7 +25023,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H47" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>25000</x:v>
@@ -25052,7 +25052,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H48" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I48" s="1">
         <x:v>20000</x:v>
@@ -25110,7 +25110,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H50" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I50" s="1">
         <x:v>5000</x:v>
@@ -25185,13 +25185,13 @@
         <x:v>14000</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -25220,7 +25220,7 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="F54" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>12</x:v>
@@ -25342,7 +25342,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H58" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I58" s="1">
         <x:v>20000</x:v>
@@ -25574,7 +25574,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H66" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I66" s="1">
         <x:v>5000</x:v>
@@ -25603,7 +25603,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H67" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I67" s="1">
         <x:v>25000</x:v>
@@ -25632,7 +25632,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H68" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I68" s="1">
         <x:v>20000</x:v>
@@ -25678,13 +25678,13 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F70" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
         <x:v>12</x:v>
@@ -25742,7 +25742,7 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="F72" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>12</x:v>
@@ -25806,7 +25806,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H74" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I74" s="1">
         <x:v>5000</x:v>
@@ -25968,13 +25968,13 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
         <x:v>12</x:v>
@@ -26154,7 +26154,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H86" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I86" s="1">
         <x:v>20000</x:v>
@@ -26241,7 +26241,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H89" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I89" s="1">
         <x:v>20000</x:v>
@@ -26299,7 +26299,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H91" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I91" s="1">
         <x:v>5000</x:v>
@@ -26328,7 +26328,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H92" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I92" s="1">
         <x:v>20000</x:v>
@@ -26386,7 +26386,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="H94" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I94" s="1">
         <x:v>300008</x:v>
@@ -26473,7 +26473,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H97" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I97" s="1">
         <x:v>25000</x:v>
@@ -26531,7 +26531,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H99" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I99" s="1">
         <x:v>20000</x:v>
@@ -26589,7 +26589,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H101" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I101" s="1">
         <x:v>25000</x:v>
@@ -26618,7 +26618,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H102" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I102" s="1">
         <x:v>20000</x:v>
@@ -26647,7 +26647,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H103" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I103" s="1">
         <x:v>5000</x:v>
@@ -26763,7 +26763,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H107" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I107" s="1">
         <x:v>20000</x:v>
@@ -26821,7 +26821,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H109" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I109" s="1">
         <x:v>25000</x:v>
@@ -26873,7 +26873,7 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="F111" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
         <x:v>12</x:v>
@@ -26908,7 +26908,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H112" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I112" s="1">
         <x:v>20000</x:v>
@@ -26995,7 +26995,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H115" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I115" s="1">
         <x:v>25000</x:v>
@@ -27070,13 +27070,13 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="D118" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E118" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F118" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G118" s="1" t="s">
         <x:v>12</x:v>
@@ -27169,7 +27169,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H121" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I121" s="1">
         <x:v>20000</x:v>
@@ -27227,7 +27227,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H123" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I123" s="1">
         <x:v>25000</x:v>
@@ -27256,7 +27256,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H124" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I124" s="1">
         <x:v>20000</x:v>
@@ -27360,13 +27360,13 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="D128" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E128" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F128" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G128" s="1" t="s">
         <x:v>12</x:v>
@@ -27401,7 +27401,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H129" s="2" t="s">
-        <x:v>761</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="I129" s="1">
         <x:v>25000</x:v>
@@ -27488,7 +27488,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H132" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I132" s="1">
         <x:v>5000</x:v>
@@ -27517,7 +27517,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H133" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I133" s="1">
         <x:v>25000</x:v>
@@ -27546,7 +27546,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H134" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I134" s="1">
         <x:v>20000</x:v>
@@ -27569,7 +27569,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F135" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G135" s="1" t="s">
         <x:v>12</x:v>
@@ -27865,7 +27865,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H145" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I145" s="1">
         <x:v>5000</x:v>
@@ -27894,7 +27894,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H146" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I146" s="1">
         <x:v>5000</x:v>
@@ -27923,7 +27923,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H147" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I147" s="1">
         <x:v>25000</x:v>
@@ -28097,7 +28097,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H153" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I153" s="1">
         <x:v>5000</x:v>
@@ -28126,7 +28126,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H154" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I154" s="1">
         <x:v>5000</x:v>
@@ -28155,7 +28155,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H155" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I155" s="1">
         <x:v>25000</x:v>
@@ -28230,13 +28230,13 @@
         <x:v>3500</x:v>
       </x:c>
       <x:c r="D158" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E158" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F158" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G158" s="1" t="s">
         <x:v>12</x:v>
@@ -28265,7 +28265,7 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="F159" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G159" s="1" t="s">
         <x:v>12</x:v>
@@ -28358,7 +28358,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H162" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I162" s="1">
         <x:v>20000</x:v>
@@ -28387,7 +28387,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H163" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I163" s="1">
         <x:v>25000</x:v>
@@ -28416,7 +28416,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H164" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I164" s="1">
         <x:v>20000</x:v>
@@ -28503,7 +28503,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H167" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I167" s="1">
         <x:v>20000</x:v>
@@ -28532,7 +28532,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H168" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I168" s="1">
         <x:v>5000</x:v>
@@ -28549,13 +28549,13 @@
         <x:v>3500</x:v>
       </x:c>
       <x:c r="D169" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E169" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F169" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G169" s="1" t="s">
         <x:v>12</x:v>
@@ -28677,7 +28677,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H173" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I173" s="1">
         <x:v>5000</x:v>
@@ -28729,7 +28729,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F175" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G175" s="1" t="s">
         <x:v>12</x:v>
@@ -28851,7 +28851,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H179" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I179" s="1">
         <x:v>20000</x:v>
@@ -28909,7 +28909,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H181" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I181" s="1">
         <x:v>25000</x:v>
@@ -28938,7 +28938,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H182" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I182" s="1">
         <x:v>20000</x:v>
@@ -29025,7 +29025,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H185" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I185" s="1">
         <x:v>25000</x:v>
@@ -29054,7 +29054,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H186" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I186" s="1">
         <x:v>20000</x:v>
@@ -29083,7 +29083,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H187" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I187" s="1">
         <x:v>5000</x:v>
@@ -29112,7 +29112,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H188" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I188" s="1">
         <x:v>5000</x:v>
@@ -29141,7 +29141,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H189" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I189" s="1">
         <x:v>25000</x:v>
@@ -29158,13 +29158,13 @@
         <x:v>3500</x:v>
       </x:c>
       <x:c r="D190" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E190" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F190" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G190" s="1" t="s">
         <x:v>12</x:v>
@@ -29257,7 +29257,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H193" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I193" s="1">
         <x:v>25000</x:v>
@@ -29303,13 +29303,13 @@
         <x:v>3500</x:v>
       </x:c>
       <x:c r="D195" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E195" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F195" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G195" s="1" t="s">
         <x:v>12</x:v>
@@ -29344,7 +29344,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H196" s="2" t="s">
-        <x:v>761</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="I196" s="1">
         <x:v>25000</x:v>
@@ -29373,7 +29373,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H197" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I197" s="1">
         <x:v>250000</x:v>
@@ -29402,7 +29402,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H198" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I198" s="1">
         <x:v>20000</x:v>
@@ -29460,7 +29460,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H200" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I200" s="1">
         <x:v>25000</x:v>
@@ -29576,7 +29576,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H204" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I204" s="1">
         <x:v>20000</x:v>
@@ -29692,7 +29692,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H208" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I208" s="1">
         <x:v>25000</x:v>
@@ -29750,7 +29750,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H210" s="2" t="s">
-        <x:v>761</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="I210" s="1">
         <x:v>25000</x:v>
@@ -29837,7 +29837,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H213" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I213" s="1">
         <x:v>25000</x:v>
@@ -29866,7 +29866,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H214" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I214" s="1">
         <x:v>20000</x:v>
@@ -29982,7 +29982,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H218" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I218" s="1">
         <x:v>20000</x:v>
@@ -30040,7 +30040,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H220" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I220" s="1">
         <x:v>20000</x:v>
@@ -30127,7 +30127,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H223" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I223" s="1">
         <x:v>5000</x:v>
@@ -30156,7 +30156,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H224" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I224" s="1">
         <x:v>25000</x:v>
@@ -30185,7 +30185,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H225" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I225" s="1">
         <x:v>20000</x:v>
@@ -30272,7 +30272,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H228" s="2" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="I228" s="1">
         <x:v>25000</x:v>
@@ -30301,7 +30301,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H229" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I229" s="1">
         <x:v>20000</x:v>
@@ -30446,7 +30446,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H234" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I234" s="1">
         <x:v>20000</x:v>
@@ -30498,7 +30498,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F236" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G236" s="1" t="s">
         <x:v>12</x:v>
@@ -30550,7 +30550,7 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="D238" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E238" s="1" t="s">
         <x:v>681</x:v>
@@ -30562,7 +30562,7 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="H238" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I238" s="1">
         <x:v>15000</x:v>
@@ -30794,7 +30794,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H246" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I246" s="1">
         <x:v>5000</x:v>
@@ -30939,7 +30939,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H251" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I251" s="1">
         <x:v>20000</x:v>
@@ -30997,7 +30997,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H253" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I253" s="1">
         <x:v>20000</x:v>
@@ -31084,7 +31084,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="H256" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I256" s="1">
         <x:v>5000</x:v>
@@ -34888,7 +34888,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
         <x:v>12</x:v>
@@ -35043,13 +35043,13 @@
         <x:v>5800</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>12</x:v>
@@ -35118,7 +35118,7 @@
         <x:v>398</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>12</x:v>
@@ -35141,7 +35141,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -35371,7 +35371,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>12</x:v>
@@ -35601,7 +35601,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>12</x:v>
@@ -35716,7 +35716,7 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -35946,7 +35946,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
         <x:v>12</x:v>
@@ -36038,7 +36038,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F56" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>12</x:v>
@@ -36199,7 +36199,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F63" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
         <x:v>12</x:v>
@@ -36337,7 +36337,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F69" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
         <x:v>12</x:v>
@@ -36544,7 +36544,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
         <x:v>12</x:v>
@@ -36613,7 +36613,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F81" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
         <x:v>12</x:v>
@@ -36705,7 +36705,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F85" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
         <x:v>12</x:v>
@@ -36745,13 +36745,13 @@
         <x:v>3500</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F87" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
         <x:v>12</x:v>
@@ -36791,13 +36791,13 @@
         <x:v>3300</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
         <x:v>12</x:v>
@@ -37050,7 +37050,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F100" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
         <x:v>12</x:v>
@@ -37188,7 +37188,7 @@
         <x:v>403</x:v>
       </x:c>
       <x:c r="F106" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
         <x:v>12</x:v>
@@ -37487,7 +37487,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F119" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G119" s="1" t="s">
         <x:v>12</x:v>
@@ -37665,13 +37665,13 @@
         <x:v>20600</x:v>
       </x:c>
       <x:c r="D127" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E127" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F127" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G127" s="1" t="s">
         <x:v>12</x:v>
@@ -37740,7 +37740,7 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="F130" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G130" s="1" t="s">
         <x:v>12</x:v>
@@ -37970,7 +37970,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F140" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G140" s="1" t="s">
         <x:v>12</x:v>
@@ -38039,7 +38039,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F143" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G143" s="1" t="s">
         <x:v>12</x:v>
@@ -38062,7 +38062,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F144" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G144" s="1" t="s">
         <x:v>12</x:v>
@@ -38545,7 +38545,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F165" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G165" s="1" t="s">
         <x:v>12</x:v>
@@ -38723,13 +38723,13 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="D173" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E173" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F173" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G173" s="1" t="s">
         <x:v>12</x:v>
@@ -38752,7 +38752,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F174" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G174" s="1" t="s">
         <x:v>12</x:v>
@@ -38815,13 +38815,13 @@
         <x:v>6600</x:v>
       </x:c>
       <x:c r="D177" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E177" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F177" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G177" s="1" t="s">
         <x:v>12</x:v>
@@ -38936,7 +38936,7 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="F182" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G182" s="1" t="s">
         <x:v>12</x:v>
@@ -39074,7 +39074,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F188" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G188" s="1" t="s">
         <x:v>12</x:v>
@@ -39091,13 +39091,13 @@
         <x:v>3500</x:v>
       </x:c>
       <x:c r="D189" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E189" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F189" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G189" s="1" t="s">
         <x:v>12</x:v>
@@ -39511,7 +39511,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F207" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G207" s="1" t="s">
         <x:v>12</x:v>
@@ -39534,7 +39534,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F208" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G208" s="1" t="s">
         <x:v>12</x:v>
@@ -39672,7 +39672,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F214" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G214" s="1" t="s">
         <x:v>12</x:v>
@@ -39787,7 +39787,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F219" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G219" s="1" t="s">
         <x:v>12</x:v>
@@ -39804,13 +39804,13 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="D220" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E220" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F220" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G220" s="1" t="s">
         <x:v>12</x:v>
@@ -40172,13 +40172,13 @@
         <x:v>3300</x:v>
       </x:c>
       <x:c r="D236" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E236" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F236" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G236" s="1" t="s">
         <x:v>12</x:v>
@@ -40799,7 +40799,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F263" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G263" s="1" t="s">
         <x:v>12</x:v>
@@ -40914,7 +40914,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F268" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G268" s="1" t="s">
         <x:v>12</x:v>
@@ -41236,7 +41236,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F282" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G282" s="1" t="s">
         <x:v>12</x:v>
@@ -41397,7 +41397,7 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="F289" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G289" s="1" t="s">
         <x:v>12</x:v>
@@ -41667,13 +41667,13 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="D301" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E301" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F301" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G301" s="1" t="s">
         <x:v>12</x:v>
@@ -41719,7 +41719,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F303" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G303" s="1" t="s">
         <x:v>12</x:v>
@@ -41880,7 +41880,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F310" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G310" s="1" t="s">
         <x:v>12</x:v>
@@ -42472,13 +42472,13 @@
         <x:v>13600</x:v>
       </x:c>
       <x:c r="D336" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E336" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F336" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G336" s="1" t="s">
         <x:v>12</x:v>
@@ -42524,7 +42524,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F338" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G338" s="1" t="s">
         <x:v>12</x:v>
@@ -42777,7 +42777,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F349" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G349" s="1" t="s">
         <x:v>12</x:v>
@@ -43007,7 +43007,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F359" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G359" s="1" t="s">
         <x:v>12</x:v>
@@ -43260,7 +43260,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F370" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G370" s="1" t="s">
         <x:v>12</x:v>
@@ -43306,7 +43306,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F372" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G372" s="1" t="s">
         <x:v>12</x:v>
@@ -43421,7 +43421,7 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="F377" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G377" s="1" t="s">
         <x:v>12</x:v>
@@ -43576,13 +43576,13 @@
         <x:v>3500</x:v>
       </x:c>
       <x:c r="D384" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E384" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F384" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G384" s="1" t="s">
         <x:v>12</x:v>
@@ -43651,7 +43651,7 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="F387" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G387" s="1" t="s">
         <x:v>12</x:v>
@@ -43812,7 +43812,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F394" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G394" s="1" t="s">
         <x:v>12</x:v>
@@ -44456,7 +44456,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F422" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G422" s="1" t="s">
         <x:v>12</x:v>
@@ -44657,13 +44657,13 @@
         <x:v>-2500</x:v>
       </x:c>
       <x:c r="D431" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E431" s="1" t="s">
         <x:v>288</x:v>
       </x:c>
       <x:c r="F431" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="G431" s="1" t="s">
         <x:v>88</x:v>
@@ -44709,7 +44709,7 @@
         <x:v>398</x:v>
       </x:c>
       <x:c r="F433" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G433" s="1" t="s">
         <x:v>12</x:v>
@@ -44887,13 +44887,13 @@
         <x:v>6800</x:v>
       </x:c>
       <x:c r="D441" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E441" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F441" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G441" s="1" t="s">
         <x:v>12</x:v>
@@ -45146,7 +45146,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F452" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G452" s="1" t="s">
         <x:v>12</x:v>
@@ -45215,7 +45215,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F455" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G455" s="1" t="s">
         <x:v>12</x:v>
@@ -45445,7 +45445,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F465" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G465" s="1" t="s">
         <x:v>12</x:v>
@@ -45836,7 +45836,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F482" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G482" s="1" t="s">
         <x:v>12</x:v>
@@ -45859,7 +45859,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F483" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G483" s="1" t="s">
         <x:v>12</x:v>
@@ -45882,7 +45882,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F484" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G484" s="1" t="s">
         <x:v>12</x:v>
@@ -46112,7 +46112,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F494" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G494" s="1" t="s">
         <x:v>12</x:v>
@@ -46198,13 +46198,13 @@
         <x:v>3500</x:v>
       </x:c>
       <x:c r="D498" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E498" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F498" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G498" s="1" t="s">
         <x:v>12</x:v>
@@ -46474,13 +46474,13 @@
         <x:v>6250</x:v>
       </x:c>
       <x:c r="D510" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E510" s="1" t="s">
         <x:v>288</x:v>
       </x:c>
       <x:c r="F510" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="G510" s="1" t="s">
         <x:v>88</x:v>
@@ -46589,13 +46589,13 @@
         <x:v>6800</x:v>
       </x:c>
       <x:c r="D515" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E515" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F515" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G515" s="1" t="s">
         <x:v>12</x:v>
@@ -46687,7 +46687,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F519" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G519" s="1" t="s">
         <x:v>12</x:v>
@@ -47262,7 +47262,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F544" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G544" s="1" t="s">
         <x:v>12</x:v>
@@ -47446,7 +47446,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F552" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G552" s="1" t="s">
         <x:v>12</x:v>
@@ -47469,7 +47469,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F553" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G553" s="1" t="s">
         <x:v>12</x:v>
@@ -47538,7 +47538,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F556" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G556" s="1" t="s">
         <x:v>12</x:v>
@@ -47561,7 +47561,7 @@
         <x:v>403</x:v>
       </x:c>
       <x:c r="F557" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G557" s="1" t="s">
         <x:v>12</x:v>
@@ -47653,7 +47653,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F561" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G561" s="1" t="s">
         <x:v>12</x:v>
@@ -47923,13 +47923,13 @@
         <x:v>3300</x:v>
       </x:c>
       <x:c r="D573" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E573" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F573" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G573" s="1" t="s">
         <x:v>12</x:v>
@@ -47952,7 +47952,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F574" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G574" s="1" t="s">
         <x:v>12</x:v>
@@ -48067,7 +48067,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F579" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G579" s="1" t="s">
         <x:v>12</x:v>
@@ -48590,7 +48590,7 @@
         <x:v>5600</x:v>
       </x:c>
       <x:c r="D602" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E602" s="1" t="s">
         <x:v>681</x:v>
@@ -48918,7 +48918,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F616" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G616" s="1" t="s">
         <x:v>12</x:v>
@@ -49010,7 +49010,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F620" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G620" s="1" t="s">
         <x:v>12</x:v>
@@ -49050,7 +49050,7 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="D622" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E622" s="1" t="s">
         <x:v>681</x:v>
@@ -49234,13 +49234,13 @@
         <x:v>6600</x:v>
       </x:c>
       <x:c r="D630" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E630" s="1" t="s">
         <x:v>288</x:v>
       </x:c>
       <x:c r="F630" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="G630" s="1" t="s">
         <x:v>88</x:v>
@@ -49470,7 +49470,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F640" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G640" s="1" t="s">
         <x:v>12</x:v>
@@ -49861,7 +49861,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F657" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G657" s="1" t="s">
         <x:v>12</x:v>
@@ -50091,7 +50091,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F667" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G667" s="1" t="s">
         <x:v>12</x:v>
@@ -50229,7 +50229,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F673" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G673" s="1" t="s">
         <x:v>12</x:v>
@@ -50574,7 +50574,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F688" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G688" s="1" t="s">
         <x:v>12</x:v>
@@ -50620,7 +50620,7 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="F690" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G690" s="1" t="s">
         <x:v>12</x:v>
@@ -50804,7 +50804,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="F698" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G698" s="1" t="s">
         <x:v>12</x:v>
@@ -50844,13 +50844,13 @@
         <x:v>5800</x:v>
       </x:c>
       <x:c r="D700" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E700" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F700" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G700" s="1" t="s">
         <x:v>12</x:v>
@@ -50873,7 +50873,7 @@
         <x:v>398</x:v>
       </x:c>
       <x:c r="F701" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G701" s="1" t="s">
         <x:v>12</x:v>
